--- a/data/trans_orig/P37C3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son efectivas en 2023</t>
+          <t>Población según la creencia de que las vacunas son efectivas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>38922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,82 +971,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>25567</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>42498</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>44980</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>27943</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>67840</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>9,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>25567</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>41829</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>44980</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>29524</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>66697</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85195</t>
+          <t>87120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144994</t>
+          <t>145431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>43054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78883</t>
+          <t>78280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139387</t>
+          <t>139567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207639</t>
+          <t>210586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227552</t>
+          <t>229660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292921</t>
+          <t>292590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201135</t>
+          <t>201780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242482</t>
+          <t>243817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449947</t>
+          <t>447754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>523756</t>
+          <t>527197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>19501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>47196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>26824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64386</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79969</t>
+          <t>78805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123184</t>
+          <t>123579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>51508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107541</t>
+          <t>106777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136245</t>
+          <t>137036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214808</t>
+          <t>216431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258976</t>
+          <t>256707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303834</t>
+          <t>306451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377634</t>
+          <t>378065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>444845</t>
+          <t>441583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>652119</t>
+          <t>648700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>751199</t>
+          <t>742679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46965</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60142</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99878</t>
+          <t>99044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137253</t>
+          <t>139046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92139</t>
+          <t>91271</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>121604</t>
+          <t>120605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>201174</t>
+          <t>200579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>250737</t>
+          <t>249653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>347716</t>
+          <t>348324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>390593</t>
+          <t>390424</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>402606</t>
+          <t>403530</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>434242</t>
+          <t>434598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>759079</t>
+          <t>764194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>815604</t>
+          <t>818328</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>41708</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>51621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>34284</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80057</t>
+          <t>80459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64445</t>
+          <t>70399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>214129</t>
+          <t>211670</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119631</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162381</t>
+          <t>164713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>165470</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>353189</t>
+          <t>354282</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>618234</t>
+          <t>620460</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>800538</t>
+          <t>792106</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>502206</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>555782</t>
+          <t>555853</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1149623</t>
+          <t>1146754</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1386922</t>
+          <t>1372536</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,42 +3513,42 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,01%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>5817</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44488</t>
+          <t>46567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26075</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41392</t>
+          <t>41781</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>66479</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>105579</t>
+          <t>104918</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>141955</t>
+          <t>142461</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>110203</t>
+          <t>108495</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>139198</t>
+          <t>139108</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>223548</t>
+          <t>220716</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>270347</t>
+          <t>268118</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>371472</t>
+          <t>370008</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>411819</t>
+          <t>412449</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>378170</t>
+          <t>378479</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>409058</t>
+          <t>409470</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>761753</t>
+          <t>763128</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>814198</t>
+          <t>813052</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>419</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>51626</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>89630</t>
+          <t>88787</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>31067</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>134663</t>
+          <t>134230</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>83496</t>
+          <t>88875</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>211919</t>
+          <t>210419</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>252676</t>
+          <t>252432</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>279972</t>
+          <t>280456</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>433770</t>
+          <t>432289</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>565011</t>
+          <t>559084</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>698718</t>
+          <t>699233</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>860910</t>
+          <t>853251</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>517</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>43886</t>
+          <t>43809</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>65285</t>
+          <t>64887</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71503</t>
+          <t>71509</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>94746</t>
+          <t>95448</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>121812</t>
+          <t>121410</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>152681</t>
+          <t>152551</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>201798</t>
+          <t>202444</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>224808</t>
+          <t>224382</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>306178</t>
+          <t>306109</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>331383</t>
+          <t>331603</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>514844</t>
+          <t>516851</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>548900</t>
+          <t>550451</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>32959</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>70136</t>
+          <t>69553</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>132818</t>
+          <t>132856</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>205386</t>
+          <t>207348</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>109619</t>
+          <t>111912</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>168865</t>
+          <t>169206</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>265628</t>
+          <t>261405</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>358573</t>
+          <t>354722</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>557138</t>
+          <t>554366</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>807825</t>
+          <t>804524</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>559535</t>
+          <t>570025</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>752243</t>
+          <t>754026</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1232914</t>
+          <t>1207697</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1531337</t>
+          <t>1522007</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2396887</t>
+          <t>2399194</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2717496</t>
+          <t>2703046</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2701033</t>
+          <t>2701061</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2930938</t>
+          <t>2928813</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5135309</t>
+          <t>5141782</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5519165</t>
+          <t>5538950</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>48620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25567</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42498</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>44980</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>35444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>78561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>113345</t>
+          <t>112582</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87120</t>
+          <t>85098</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145431</t>
+          <t>141015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59774</t>
+          <t>68638</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>51692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78280</t>
+          <t>90464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>173119</t>
+          <t>181220</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139567</t>
+          <t>150756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210586</t>
+          <t>221723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>263056</t>
+          <t>259143</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229660</t>
+          <t>229661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292590</t>
+          <t>288202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>223216</t>
+          <t>262234</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201780</t>
+          <t>238204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243817</t>
+          <t>283241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>486272</t>
+          <t>521378</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447754</t>
+          <t>478999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>527197</t>
+          <t>555558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>51756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>31136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>46696</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65807</t>
+          <t>73223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>116522</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>93188</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123579</t>
+          <t>143496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>83778</t>
+          <t>96516</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>79338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106777</t>
+          <t>118408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>183868</t>
+          <t>213038</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137036</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216431</t>
+          <t>243529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>282160</t>
+          <t>313512</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256707</t>
+          <t>284474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306451</t>
+          <t>337818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>404084</t>
+          <t>377084</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378065</t>
+          <t>353235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441583</t>
+          <t>395247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>686244</t>
+          <t>690596</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>648700</t>
+          <t>658033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>742679</t>
+          <t>722404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>420446</t>
+          <t>473885</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>420446</t>
+          <t>473885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>420446</t>
+          <t>473885</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>509732</t>
+          <t>499320</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>509732</t>
+          <t>499320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>509732</t>
+          <t>499320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>930178</t>
+          <t>973205</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>930178</t>
+          <t>973205</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>930178</t>
+          <t>973205</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>758</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33340</t>
+          <t>41504</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>58763</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18693</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>72665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>117933</t>
+          <t>138281</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99044</t>
+          <t>117380</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>139046</t>
+          <t>161378</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>106065</t>
+          <t>127303</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91271</t>
+          <t>110631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120605</t>
+          <t>145996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>223998</t>
+          <t>265583</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>200579</t>
+          <t>239201</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249653</t>
+          <t>296045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>370387</t>
+          <t>423688</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348324</t>
+          <t>396834</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>390424</t>
+          <t>446086</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>419014</t>
+          <t>474006</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>403530</t>
+          <t>456108</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>434598</t>
+          <t>492269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>789400</t>
+          <t>897694</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>764194</t>
+          <t>863719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>818328</t>
+          <t>925732</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>540787</t>
+          <t>619826</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>540787</t>
+          <t>619826</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>540787</t>
+          <t>619826</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1074076</t>
+          <t>1234751</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1074076</t>
+          <t>1234751</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1074076</t>
+          <t>1234751</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25512</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41708</t>
+          <t>40480</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22628</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51621</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>57712</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34284</t>
+          <t>49256</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80459</t>
+          <t>77306</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>146607</t>
+          <t>164639</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70399</t>
+          <t>143638</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211670</t>
+          <t>190516</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>143181</t>
+          <t>156788</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>139168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>164713</t>
+          <t>176174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>289788</t>
+          <t>321427</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>295391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>354282</t>
+          <t>352048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>699759</t>
+          <t>490708</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>620460</t>
+          <t>466205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>792106</t>
+          <t>513659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>527409</t>
+          <t>537065</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>502206</t>
+          <t>518118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>555853</t>
+          <t>557104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1227168</t>
+          <t>1027773</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1146754</t>
+          <t>995405</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1372536</t>
+          <t>1055342</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>880976</t>
+          <t>693365</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>880976</t>
+          <t>693365</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>880976</t>
+          <t>693365</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>708539</t>
+          <t>732398</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>708539</t>
+          <t>732398</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>708539</t>
+          <t>732398</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1589515</t>
+          <t>1425762</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1589515</t>
+          <t>1425762</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1589515</t>
+          <t>1425762</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,42 +3513,42 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2437</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>7333</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>6348</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,01%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -3566,22 +3566,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,22 +3601,22 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46567</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>61510</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>48247</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>76711</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>122013</t>
+          <t>136982</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>104918</t>
+          <t>117898</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>142461</t>
+          <t>157533</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>122983</t>
+          <t>135337</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>108495</t>
+          <t>121608</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>139108</t>
+          <t>153174</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>244996</t>
+          <t>272320</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>220716</t>
+          <t>245609</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>268118</t>
+          <t>297103</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>392178</t>
+          <t>419181</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>370008</t>
+          <t>396067</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>412449</t>
+          <t>440307</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>395383</t>
+          <t>441439</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>378479</t>
+          <t>423722</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>409470</t>
+          <t>458038</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>787561</t>
+          <t>860620</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>763128</t>
+          <t>833481</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>813052</t>
+          <t>888690</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>555745</t>
+          <t>603558</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>555745</t>
+          <t>603558</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>555745</t>
+          <t>603558</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>542668</t>
+          <t>605059</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>542668</t>
+          <t>605059</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>542668</t>
+          <t>605059</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1098413</t>
+          <t>1208618</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1098413</t>
+          <t>1208618</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1098413</t>
+          <t>1208618</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>668</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>19229</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>40303</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>31905</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>51626</t>
+          <t>51459</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>75519</t>
+          <t>84710</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63279</t>
+          <t>70710</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>88787</t>
+          <t>98839</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>85035</t>
+          <t>92549</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>31067</t>
+          <t>79359</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>134230</t>
+          <t>105822</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>160555</t>
+          <t>177260</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>88875</t>
+          <t>160735</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>210419</t>
+          <t>197809</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>267678</t>
+          <t>294521</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>252432</t>
+          <t>280171</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>280456</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>494109</t>
+          <t>317355</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>432289</t>
+          <t>303085</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>559084</t>
+          <t>330815</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>761787</t>
+          <t>611877</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>699233</t>
+          <t>591019</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>853251</t>
+          <t>631060</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>366488</t>
+          <t>404599</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>366488</t>
+          <t>404599</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>366488</t>
+          <t>404599</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>601299</t>
+          <t>433732</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>601299</t>
+          <t>433732</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>601299</t>
+          <t>433732</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>967787</t>
+          <t>838332</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>967787</t>
+          <t>838332</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>967787</t>
+          <t>838332</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4852,22 +4852,22 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>532</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,22 +4887,22 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>533</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>29295</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>61215</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>43809</t>
+          <t>50624</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>64887</t>
+          <t>74891</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,67 +5191,67 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>83124</t>
+          <t>89780</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>77857</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>16,93%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>150995</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>131820</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>167077</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
           <t>19,71%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>136967</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>121410</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>152551</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>213824</t>
+          <t>231673</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>202444</t>
+          <t>217197</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>224382</t>
+          <t>243614</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>319238</t>
+          <t>349157</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>306109</t>
+          <t>335157</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>331603</t>
+          <t>362376</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>533062</t>
+          <t>580830</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>516851</t>
+          <t>561408</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>550451</t>
+          <t>598899</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>421676</t>
+          <t>460009</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>421676</t>
+          <t>460009</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>421676</t>
+          <t>460009</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>700814</t>
+          <t>765897</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>700814</t>
+          <t>765897</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>700814</t>
+          <t>765897</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,102 +5499,102 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>12015</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>21796</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>13978</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>33947</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>11008</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>5785</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>21203</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>21410</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>12519</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>33850</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>51797</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,67 +5647,67 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>61582</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>48062</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>78088</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>54540</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>41756</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>69553</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>171711</t>
+          <t>201650</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>132856</t>
+          <t>170487</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>207348</t>
+          <t>235387</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>139451</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>111912</t>
+          <t>130827</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>169206</t>
+          <t>177200</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>311163</t>
+          <t>354464</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>261405</t>
+          <t>320473</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>354722</t>
+          <t>396245</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>729351</t>
+          <t>814931</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>554366</t>
+          <t>758800</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>804524</t>
+          <t>873374</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>683939</t>
+          <t>766911</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>570025</t>
+          <t>726535</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>754026</t>
+          <t>812008</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1413290</t>
+          <t>1581842</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1207697</t>
+          <t>1511301</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1522007</t>
+          <t>1650635</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2489042</t>
+          <t>2432427</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2399194</t>
+          <t>2372909</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2703046</t>
+          <t>2494912</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2782451</t>
+          <t>2758340</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2701061</t>
+          <t>2711924</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2928813</t>
+          <t>2804954</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>5271493</t>
+          <t>5190767</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5141782</t>
+          <t>5114348</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5538950</t>
+          <t>5263986</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
